--- a/task/tasklist.xlsx
+++ b/task/tasklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alantop_dir\alantop_data\alantop_git\github\task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9F9475-59F3-47A4-853B-A9B7B3E4BE87}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7132A82-6900-4B8A-BACD-4BDD5D9EEBEB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>办理银行卡</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,6 +92,14 @@
   </si>
   <si>
     <t>交回执，领蓝卡 8.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人脸轨迹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻oracle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.44140625" bestFit="1" customWidth="1"/>
@@ -507,6 +515,16 @@
         <v>13</v>
       </c>
     </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
